--- a/data-raw/workbooks/kelpbio-1-full-macro.xlsx
+++ b/data-raw/workbooks/kelpbio-1-full-macro.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="weight" sheetId="1" r:id="rId1"/>
-    <sheet name="size" sheetId="2" r:id="rId2"/>
+    <sheet name="size_census" sheetId="2" r:id="rId2"/>
     <sheet name="survey" sheetId="3" r:id="rId3"/>
     <sheet name="canopy" sheetId="4" r:id="rId4"/>
     <sheet name="wetdry" sheetId="5" r:id="rId5"/>
